--- a/Strings/data.xlsx
+++ b/Strings/data.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Data1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,4 +496,17 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Strings/data.xlsx
+++ b/Strings/data.xlsx
@@ -1,35 +1,104 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\pythonF\Strings\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CCBFC5B-9B43-424A-9B3C-64AB0A1B622A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Data1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Data2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Data1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Naveen</author>
+  </authors>
+  <commentList>
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>This is a comment</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>A@gmail.com</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>B@gmail.com</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>C@gmail.com</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,91 +117,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="t1" displayName="t1" ref="A1:C4" headerRowCount="1">
-  <autoFilter ref="A1:C2"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Name"/>
-    <tableColumn id="2" name="Age"/>
-    <tableColumn id="3" name="Email"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="t1" displayName="t1_" ref="A1:D4">
+  <autoFilter ref="A1:D4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Age"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Email"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Gender"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -420,93 +432,76 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
         <v>23</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>A@gmail.com</t>
-        </is>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
         <v>24</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>B@gmail.com</t>
-        </is>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
         <v>24</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CD@gmail.com</t>
-        </is>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"Male,Female"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>